--- a/backend/data/upi_admin_log.xlsx
+++ b/backend/data/upi_admin_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,6 +487,41 @@
         <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-06 13:15:37</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>abhinav7786@gmail.com</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>arjun.patel@okaxis</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>53b5ac53668c9bcf65bc04547df7a37737606281a54ddbb43b9b605e0b91c615</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>127.0.0.1</t>
         </is>
